--- a/artfynd/A 25724-2022 artfynd.xlsx
+++ b/artfynd/A 25724-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25724-2022 artfynd.xlsx
+++ b/artfynd/A 25724-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17191310</v>
+        <v>17191304</v>
       </c>
       <c r="B2" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4189</v>
+        <v>1445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -721,17 +716,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skirkällan 250 m so, Srm</t>
+          <t>Skirkällan 300 m so, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581167.4686999102</v>
+        <v>581134</v>
       </c>
       <c r="R2" t="n">
-        <v>6535975.010487799</v>
+        <v>6535955</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,24 +753,9 @@
           <t>2015-03-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>fjolårsex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,6 +785,124 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>17191310</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skirkällan 250 m so, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>581167</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6535975</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lerbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>fjolårsex</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Grandominerad blandskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25724-2022 artfynd.xlsx
+++ b/artfynd/A 25724-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17191304</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,8 +913,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17191310</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>